--- a/审核导出/lamination_material_审核.xlsx
+++ b/审核导出/lamination_material_审核.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,9 +524,21 @@
           <t>普通光膠</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>一般過膠產品通用光膠</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -545,14 +557,22 @@
           <t>預塗光膠</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>5um</t>
-        </is>
-      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>預塗光膠，適用於一般過膠產品</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>華一 / HY1205</t>
@@ -570,14 +590,22 @@
           <t>預塗光膠</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8um</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>預塗光膠，適用於平裝書封面過膠</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>華一 / HY1208</t>
@@ -595,14 +623,22 @@
           <t>超粘預塗光膠</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10um</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>超粘預塗光膠，適用於需擊凹凸/壓紋等後加工</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>華一 / HY1210</t>
@@ -620,14 +656,22 @@
           <t>預塗單面電暈光膠</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8um</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>預塗單面電暈光膠，特殊表面處理用</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>HF G20-S / HY65(HY1208單面電暈薄</t>
@@ -645,9 +689,21 @@
           <t>水性尼龍光膠</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>水性尼龍光膠，尼龍材質覆膜</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -666,14 +722,22 @@
           <t>預塗尼龍光膠</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17um</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>預塗尼龍光膠，尼龍材質覆膜</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>KNGS1217</t>
@@ -691,9 +755,21 @@
           <t>水性PET光膠</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>水性PET光膠，PET材質覆膜</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -712,14 +788,22 @@
           <t>預塗PET光膠</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10um</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>預塗PET光膠</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>康得-菲爾 / PET1210</t>
@@ -737,14 +821,22 @@
           <t>預塗PET光膠</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8um</t>
-        </is>
-      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>預塗PET光膠（電暈值不穩定，注意測試）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>HF0808 / HY0808</t>
@@ -762,14 +854,22 @@
           <t>預塗抗靜電光膠</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13um</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>預塗抗靜電光膠，防靜電需求產品</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>HY40 / （1213抗靜電超粘）</t>
@@ -787,9 +887,21 @@
           <t>水性耐磨光膠</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>水性耐磨光膠，需耐磨產品</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -808,14 +920,22 @@
           <t>預塗耐磨光膠</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10um</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>預塗耐磨光膠，需耐磨產品</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>騰錦 / 6018A</t>
@@ -833,14 +953,22 @@
           <t>預塗普通耐磨啞膠 / （耐磨性能：2磅50次有輕微磨花）</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>10um</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>預塗普通耐磨啞膠（耐磨：2磅50次輕微磨花）</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>啞膠</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>啞面</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>康得新 / KPMB-F</t>
@@ -858,14 +986,22 @@
           <t>預塗平價高耐磨啞膠 / （耐磨性能：4磅50次無磨花）</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10um</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>預塗平價高耐磨啞膠（耐磨：4磅50次無磨花）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>啞膠</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>啞面</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>鑫達中天 / YT008A</t>
@@ -883,14 +1019,22 @@
           <t>預塗高耐磨啞膠 / （耐磨性能：4磅50次無磨花）</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10um</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>預塗高耐磨啞膠（耐磨：4磅50次無磨花）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>啞膠</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>啞面</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>鑫達中天 / TN008</t>
@@ -908,14 +1052,22 @@
           <t>預塗柔感啞膠</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10um</t>
-        </is>
-      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>預塗柔感啞膠，柔軟觸感效果</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>啞膠</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>啞面</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>騰錦 / 6015A</t>
@@ -933,9 +1085,21 @@
           <t>透明鐳射菲林</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>透明鐳射菲林，特殊鐳射效果覆膜</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -944,13 +1108,187 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>#FL-99901</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>水性單面電暈光膠</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>水性單面電暈光膠，單面電暈處理</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>光膠</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>透明</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>#FL-99902</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>普通啞膠</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>一般過膠產品啞膠（無壓紋）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>啞膠</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>啞面</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>#FL-99903</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>預塗啞膠</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>預塗啞膠，適用於一般過膠產品（無擊凹凸、壓紋）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>啞膠</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>啞面</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>#FL-99904</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>預塗啞膠</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>預塗啞膠，適用於平裝書封面過膠（無擊凹凸、壓紋）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>啞膠</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>啞面</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>#FL-99905</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>超粘預塗啞膠</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>超粘預塗啞膠，適用於需擊凹凸/壓紋/粗糙面</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>啞膠</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>啞面</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>#FL-99906</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>預塗抗靜電啞膠</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>預塗抗靜電啞膠，防靜電需求產品</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>啞膠</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>啞面</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -995,8 +1333,8 @@
     <col width="8" customWidth="1" min="27" max="27"/>
     <col width="10.2" customWidth="1" min="28" max="28"/>
     <col width="10.2" customWidth="1" min="29" max="29"/>
-    <col width="15.3" customWidth="1" min="30" max="30"/>
-    <col width="10.2" customWidth="1" min="31" max="31"/>
+    <col width="10.2" customWidth="1" min="30" max="30"/>
+    <col width="15.3" customWidth="1" min="31" max="31"/>
     <col width="10.2" customWidth="1" min="32" max="32"/>
     <col width="25.5" customWidth="1" min="33" max="33"/>
     <col width="22.95" customWidth="1" min="34" max="34"/>
@@ -1194,17 +1532,17 @@
       </c>
       <c r="AC1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金</t>
+          <t>立體擊凸</t>
         </is>
       </c>
       <c r="AD1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金擊凸</t>
+          <t>立體燙金</t>
         </is>
       </c>
       <c r="AE1" s="3" t="inlineStr">
         <is>
-          <t>立體擊凸</t>
+          <t>立體燙金擊凸</t>
         </is>
       </c>
       <c r="AF1" s="3" t="inlineStr">
@@ -1249,7 +1587,7 @@
       </c>
       <c r="AN1" s="3" t="inlineStr">
         <is>
-          <t>普通油墨 / （含耐晒）</t>
+          <t>普通油墨 / （含耐曬）</t>
         </is>
       </c>
       <c r="AO1" s="3" t="inlineStr">
@@ -5563,9 +5901,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AC12" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="AC12" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="AD12" s="6" t="inlineStr">
@@ -5573,9 +5911,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="AE12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AF12" s="6" t="inlineStr">
@@ -7524,19 +7862,19 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="AD17" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
+      <c r="AE17" s="7" t="inlineStr">
         <is>
           <t>O</t>
-        </is>
-      </c>
-      <c r="AE17" s="5" t="inlineStr">
-        <is>
-          <t>V</t>
         </is>
       </c>
       <c r="AF17" s="6" t="inlineStr">
@@ -8290,9 +8628,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AC19" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
         </is>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -8300,9 +8638,9 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AE19" s="5" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="AE19" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="AF19" s="6" t="inlineStr">
